--- a/data/trans_orig/P23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95412</t>
+          <t>98394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128116</t>
+          <t>132487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152051</t>
+          <t>152158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183997</t>
+          <t>183311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>258508</t>
+          <t>257841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>304945</t>
+          <t>305406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60164</t>
+          <t>58321</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>31387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51531</t>
+          <t>53051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81706</t>
+          <t>83693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92878</t>
+          <t>91965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125637</t>
+          <t>123471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51824</t>
+          <t>52951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80806</t>
+          <t>79465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153219</t>
+          <t>151088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196965</t>
+          <t>194010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164011</t>
+          <t>162993</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>208888</t>
+          <t>205559</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>339763</t>
+          <t>336941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>378489</t>
+          <t>379084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>513862</t>
+          <t>515175</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>576841</t>
+          <t>579118</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93518</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133713</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>36972</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119908</t>
+          <t>117846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164053</t>
+          <t>161280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>23031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32015</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>157569</t>
+          <t>156275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201126</t>
+          <t>199570</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>94985</t>
+          <t>93100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131117</t>
+          <t>131052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>259741</t>
+          <t>262096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>317643</t>
+          <t>318652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87806</t>
+          <t>89321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122434</t>
+          <t>123325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208313</t>
+          <t>209708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>242366</t>
+          <t>243861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304959</t>
+          <t>304045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357431</t>
+          <t>359186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51809</t>
+          <t>51272</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79610</t>
+          <t>79950</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23794</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63477</t>
+          <t>63870</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97048</t>
+          <t>97316</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13823</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27582</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36243</t>
+          <t>37281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124337</t>
+          <t>121820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158585</t>
+          <t>159087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62457</t>
+          <t>61163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92189</t>
+          <t>91207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193150</t>
+          <t>189997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241620</t>
+          <t>241479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96345</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130703</t>
+          <t>128331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>207488</t>
+          <t>210323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244208</t>
+          <t>245812</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>310710</t>
+          <t>312203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>365028</t>
+          <t>365492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61422</t>
+          <t>61322</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>91780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28413</t>
+          <t>28334</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50932</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97024</t>
+          <t>96936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137183</t>
+          <t>135220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>37984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>137661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175103</t>
+          <t>175637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79450</t>
+          <t>78022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111768</t>
+          <t>111257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226184</t>
+          <t>225822</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276515</t>
+          <t>275433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61608</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89784</t>
+          <t>91093</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>104260</t>
+          <t>104699</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>132657</t>
+          <t>133741</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>174617</t>
+          <t>175246</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>215449</t>
+          <t>214509</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32568</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>56438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>56257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89293</t>
+          <t>88177</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>68174</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95404</t>
+          <t>96505</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>43873</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>70493</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>118425</t>
+          <t>118031</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>156583</t>
+          <t>156792</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76466</t>
+          <t>76509</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107869</t>
+          <t>109290</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>176778</t>
+          <t>177062</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>206964</t>
+          <t>207813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>262804</t>
+          <t>263977</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>307618</t>
+          <t>308419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>65672</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>56417</t>
+          <t>55712</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>87236</t>
+          <t>87191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>101829</t>
+          <t>103469</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>135985</t>
+          <t>133935</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44377</t>
+          <t>44489</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>71103</t>
+          <t>71342</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>152433</t>
+          <t>153755</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>196387</t>
+          <t>197254</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>262289</t>
+          <t>263136</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>312627</t>
+          <t>312994</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>422643</t>
+          <t>419782</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>469038</t>
+          <t>466952</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>697079</t>
+          <t>697912</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>767063</t>
+          <t>770504</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>75507</t>
+          <t>74863</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>111234</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22247</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44786</t>
+          <t>45025</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>105130</t>
+          <t>105623</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>147057</t>
+          <t>146760</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16507</t>
+          <t>16081</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>18860</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>201528</t>
+          <t>200611</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>247053</t>
+          <t>250109</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>129657</t>
+          <t>130975</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>171383</t>
+          <t>173506</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>345486</t>
+          <t>341951</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>409073</t>
+          <t>409335</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>257779</t>
+          <t>259132</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>311224</t>
+          <t>311917</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>491892</t>
+          <t>491526</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>546120</t>
+          <t>545493</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>765286</t>
+          <t>764448</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>842103</t>
+          <t>847355</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>120244</t>
+          <t>122498</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>162640</t>
+          <t>163165</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>61804</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>94504</t>
+          <t>95922</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>193831</t>
+          <t>191651</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>246239</t>
+          <t>244763</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>35220</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10139</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27893</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>267985</t>
+          <t>266810</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>320799</t>
+          <t>320897</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>146611</t>
+          <t>147512</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>194091</t>
+          <t>192545</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>426434</t>
+          <t>425031</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>498382</t>
+          <t>499013</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1200076</t>
+          <t>1203141</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1310485</t>
+          <t>1316105</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2203911</t>
+          <t>2202130</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2311143</t>
+          <t>2308664</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3434762</t>
+          <t>3439197</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3594076</t>
+          <t>3600392</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>588377</t>
+          <t>584210</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>674870</t>
+          <t>674534</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>228119</t>
+          <t>227951</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>290133</t>
+          <t>286169</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>831236</t>
+          <t>831198</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>939946</t>
+          <t>939920</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>68477</t>
+          <t>70808</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>103539</t>
+          <t>106217</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>68458</t>
+          <t>68275</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>103844</t>
+          <t>102893</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>147719</t>
+          <t>145101</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>196882</t>
+          <t>197464</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1243869</t>
+          <t>1246038</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1358298</t>
+          <t>1358779</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>734097</t>
+          <t>734624</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>832959</t>
+          <t>826978</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2004640</t>
+          <t>2001220</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2158558</t>
+          <t>2163486</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62376</t>
+          <t>61284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94315</t>
+          <t>93153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129902</t>
+          <t>129955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167544</t>
+          <t>165771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200127</t>
+          <t>201383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249937</t>
+          <t>251552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65393</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96981</t>
+          <t>98026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54836</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101295</t>
+          <t>100563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141453</t>
+          <t>141257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27489</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109108</t>
+          <t>109066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144968</t>
+          <t>144525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74117</t>
+          <t>74896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111791</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193974</t>
+          <t>191318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244221</t>
+          <t>241338</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148967</t>
+          <t>149428</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>194459</t>
+          <t>194734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>284662</t>
+          <t>283484</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>330937</t>
+          <t>331475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445396</t>
+          <t>447929</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>512896</t>
+          <t>514645</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,0%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106099</t>
+          <t>106688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146812</t>
+          <t>148575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48797</t>
+          <t>50910</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80940</t>
+          <t>81975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165016</t>
+          <t>167358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215554</t>
+          <t>217417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,47 +6899,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8142</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>16113</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8142</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>15143</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>34305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173099</t>
+          <t>169780</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>217574</t>
+          <t>218029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>122183</t>
+          <t>124052</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165827</t>
+          <t>166595</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>306209</t>
+          <t>307216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371163</t>
+          <t>368086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90812</t>
+          <t>91627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124455</t>
+          <t>125605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200207</t>
+          <t>197974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236023</t>
+          <t>235930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299163</t>
+          <t>300152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>350762</t>
+          <t>351090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,87%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74656</t>
+          <t>72696</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>106427</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47612</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>104406</t>
+          <t>104381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145240</t>
+          <t>143900</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18025</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101476</t>
+          <t>101824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134451</t>
+          <t>137180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66733</t>
+          <t>66722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98430</t>
+          <t>100536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>175102</t>
+          <t>176289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223687</t>
+          <t>225113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117556</t>
+          <t>116369</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156372</t>
+          <t>155916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>219016</t>
+          <t>218074</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>257420</t>
+          <t>256706</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>347562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>401629</t>
+          <t>405101</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>88073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126240</t>
+          <t>125692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35214</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59893</t>
+          <t>59983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>132505</t>
+          <t>129990</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176120</t>
+          <t>174861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19842</t>
+          <t>19676</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30928</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98924</t>
+          <t>103384</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139019</t>
+          <t>140079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80602</t>
+          <t>81161</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115353</t>
+          <t>115464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>192137</t>
+          <t>194796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245773</t>
+          <t>247554</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56016</t>
+          <t>56782</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85081</t>
+          <t>84789</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111495</t>
+          <t>114783</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>142199</t>
+          <t>143046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>175418</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219640</t>
+          <t>219060</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64572</t>
+          <t>64862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>17942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37953</t>
+          <t>38673</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60679</t>
+          <t>61576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>94951</t>
+          <t>93816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74166</t>
+          <t>72486</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>106005</t>
+          <t>103205</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>48619</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>75032</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>130339</t>
+          <t>130801</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>170215</t>
+          <t>170752</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88416</t>
+          <t>87651</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>120698</t>
+          <t>123138</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>173689</t>
+          <t>174671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>205673</t>
+          <t>205671</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271275</t>
+          <t>271697</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>318144</t>
+          <t>319419</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71390</t>
+          <t>71196</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102117</t>
+          <t>102703</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>90903</t>
+          <t>89369</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>129145</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17133</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62003</t>
+          <t>61820</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92554</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>45745</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>115506</t>
+          <t>115138</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>154329</t>
+          <t>154746</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>187794</t>
+          <t>187341</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>239777</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>379850</t>
+          <t>380274</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>432667</t>
+          <t>434396</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>578803</t>
+          <t>580690</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>654727</t>
+          <t>654673</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>148407</t>
+          <t>147138</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>192841</t>
+          <t>194440</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>75573</t>
+          <t>74998</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>111287</t>
+          <t>112528</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>228809</t>
+          <t>231367</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>295894</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35444</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>13421</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>33009</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>32373</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>60721</t>
+          <t>60353</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>231915</t>
+          <t>229736</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>282960</t>
+          <t>285693</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>150048</t>
+          <t>151143</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>197695</t>
+          <t>197532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>393474</t>
+          <t>395463</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>465249</t>
+          <t>465384</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>320284</t>
+          <t>321806</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>378794</t>
+          <t>379592</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>518653</t>
+          <t>519870</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>573043</t>
+          <t>573281</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>858323</t>
+          <t>857980</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>937472</t>
+          <t>937076</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>110498</t>
+          <t>108898</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>155696</t>
+          <t>155403</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>52319</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>82900</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>170585</t>
+          <t>171930</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>229452</t>
+          <t>228198</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26999</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>38221</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>251556</t>
+          <t>251848</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>305849</t>
+          <t>306470</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>174972</t>
+          <t>178072</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>225650</t>
+          <t>227275</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>442933</t>
+          <t>442422</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>519141</t>
+          <t>516546</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1169218</t>
+          <t>1174886</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1285685</t>
+          <t>1295126</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2123877</t>
+          <t>2127896</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2246418</t>
+          <t>2245641</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3322320</t>
+          <t>3339155</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3501530</t>
+          <t>3508414</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>783459</t>
+          <t>787449</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>893771</t>
+          <t>889698</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>356331</t>
+          <t>355637</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>430372</t>
+          <t>430250</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1169229</t>
+          <t>1170752</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1298826</t>
+          <t>1299146</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>76477</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>119316</t>
+          <t>116998</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>55338</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>94330</t>
+          <t>91729</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>144947</t>
+          <t>145511</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>199703</t>
+          <t>199524</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1201751</t>
+          <t>1208657</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1322573</t>
+          <t>1318921</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>848762</t>
+          <t>846545</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>958163</t>
+          <t>954179</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2080245</t>
+          <t>2085102</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2251549</t>
+          <t>2241909</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco y/o marihuana/hachís, actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89292</t>
+          <t>88679</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123890</t>
+          <t>124050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141631</t>
+          <t>143183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174394</t>
+          <t>177593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>239536</t>
+          <t>240308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291220</t>
+          <t>291676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>64543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96016</t>
+          <t>95727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70671</t>
+          <t>68685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113515</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154265</t>
+          <t>154059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>11818</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>29469</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79977</t>
+          <t>81532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115183</t>
+          <t>116061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>52582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81162</t>
+          <t>80028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139324</t>
+          <t>141507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183212</t>
+          <t>186210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11870,12 +11870,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184363</t>
+          <t>184514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>229688</t>
+          <t>228072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>314440</t>
+          <t>316887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>360494</t>
+          <t>361242</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>511724</t>
+          <t>516454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>580636</t>
+          <t>580385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68971</t>
+          <t>69477</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103430</t>
+          <t>103827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27407</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52927</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104409</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>144932</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174145</t>
+          <t>170179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>219295</t>
+          <t>217166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117137</t>
+          <t>116143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159160</t>
+          <t>158200</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>302990</t>
+          <t>304525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>365981</t>
+          <t>361782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134780</t>
+          <t>134949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169487</t>
+          <t>170109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206940</t>
+          <t>206365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240414</t>
+          <t>240724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>351413</t>
+          <t>351995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401415</t>
+          <t>400913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>56504</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84072</t>
+          <t>84395</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21129</t>
+          <t>20576</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>40949</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83215</t>
+          <t>83321</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119849</t>
+          <t>119078</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73011</t>
+          <t>73949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103066</t>
+          <t>106609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61130</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91577</t>
+          <t>91754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142557</t>
+          <t>143409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186315</t>
+          <t>186373</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110230</t>
+          <t>110710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150276</t>
+          <t>148807</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206156</t>
+          <t>206854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245270</t>
+          <t>247618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>325813</t>
+          <t>329792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>385556</t>
+          <t>384924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82429</t>
+          <t>82791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117094</t>
+          <t>114787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38474</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>64607</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127289</t>
+          <t>127226</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>172536</t>
+          <t>173284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13351,12 +13351,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115782</t>
+          <t>115868</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>154033</t>
+          <t>154370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114983</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>202736</t>
+          <t>201456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252936</t>
+          <t>254799</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66927</t>
+          <t>67907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>96575</t>
+          <t>94964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>125987</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>152506</t>
+          <t>154015</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>201315</t>
+          <t>200079</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241749</t>
+          <t>241819</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13807,12 +13807,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,26%</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55464</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82679</t>
+          <t>82491</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13920,12 +13920,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13983,12 +13983,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14033,12 +14033,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66306</t>
+          <t>66456</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95685</t>
+          <t>94130</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>44876</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14131,12 +14131,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>118165</t>
+          <t>117804</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>157672</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14146,12 +14146,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107446</t>
+          <t>107464</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138864</t>
+          <t>138687</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>167301</t>
+          <t>166695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>197907</t>
+          <t>196765</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>284693</t>
+          <t>284782</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>329227</t>
+          <t>327903</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63898</t>
+          <t>63603</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25513</t>
+          <t>26280</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82014</t>
+          <t>82930</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70485</t>
+          <t>70498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>100964</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>51587</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>79504</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>130783</t>
+          <t>131382</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>171106</t>
+          <t>172929</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>295804</t>
+          <t>292686</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>349453</t>
+          <t>347043</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>401593</t>
+          <t>399516</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>449987</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>709713</t>
+          <t>709090</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>783399</t>
+          <t>785011</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>109418</t>
+          <t>110496</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>156583</t>
+          <t>152296</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>71166</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>105026</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>189763</t>
+          <t>192289</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>245484</t>
+          <t>247682</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12700</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31946</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34615</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>59063</t>
+          <t>58163</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>157956</t>
+          <t>157626</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>206882</t>
+          <t>204165</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>130620</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>175064</t>
+          <t>174231</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>301491</t>
+          <t>301095</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>367329</t>
+          <t>368335</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>355894</t>
+          <t>353266</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>410843</t>
+          <t>413578</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>496664</t>
+          <t>495769</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>553574</t>
+          <t>552576</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15479,12 +15479,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>864459</t>
+          <t>867998</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>945155</t>
+          <t>947181</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>121065</t>
+          <t>119377</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>165344</t>
+          <t>168070</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>68268</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>106968</t>
+          <t>109203</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200174</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>257675</t>
+          <t>257220</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>31774</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20817</t>
+          <t>20539</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>43446</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>210227</t>
+          <t>209440</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>263854</t>
+          <t>263021</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>181320</t>
+          <t>181056</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>231796</t>
+          <t>229852</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>407534</t>
+          <t>404796</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>479082</t>
+          <t>476639</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1441327</t>
+          <t>1442904</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1558000</t>
+          <t>1559712</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2163871</t>
+          <t>2173783</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2283319</t>
+          <t>2285609</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3646002</t>
+          <t>3647684</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3815399</t>
+          <t>3820062</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>652111</t>
+          <t>654103</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>748100</t>
+          <t>747566</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1028560</t>
+          <t>1022622</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1148926</t>
+          <t>1149943</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>74832</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>113295</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>141584</t>
+          <t>143390</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>193116</t>
+          <t>196425</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1040643</t>
+          <t>1038811</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1154044</t>
+          <t>1152918</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>801808</t>
+          <t>797859</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>902935</t>
+          <t>901243</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1867999</t>
+          <t>1866753</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2024678</t>
+          <t>2020665</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P23-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98394</t>
+          <t>96396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132487</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152158</t>
+          <t>152305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>183311</t>
+          <t>183771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>257841</t>
+          <t>257394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305406</t>
+          <t>303650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58321</t>
+          <t>60547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>11737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31387</t>
+          <t>29714</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53051</t>
+          <t>52888</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83693</t>
+          <t>83315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91965</t>
+          <t>91628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123471</t>
+          <t>124824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52951</t>
+          <t>51648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>81616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151088</t>
+          <t>152370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194010</t>
+          <t>196235</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,76%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>162993</t>
+          <t>165227</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205559</t>
+          <t>210618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>336941</t>
+          <t>338054</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>379084</t>
+          <t>377335</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>515175</t>
+          <t>516572</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>579118</t>
+          <t>578582</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134333</t>
+          <t>134429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117846</t>
+          <t>119596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161280</t>
+          <t>163887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23031</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>156275</t>
+          <t>155125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>199570</t>
+          <t>201102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93100</t>
+          <t>94765</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>130477</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>262096</t>
+          <t>261505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>318652</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89321</t>
+          <t>91391</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123325</t>
+          <t>123716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>209708</t>
+          <t>209012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>243861</t>
+          <t>243485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304045</t>
+          <t>306422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359186</t>
+          <t>356728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51272</t>
+          <t>51047</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79950</t>
+          <t>80593</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>23949</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63870</t>
+          <t>63847</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97316</t>
+          <t>96853</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>36072</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121820</t>
+          <t>123300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159087</t>
+          <t>159184</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61163</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91207</t>
+          <t>92361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189997</t>
+          <t>193782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241479</t>
+          <t>242310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94582</t>
+          <t>96145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128331</t>
+          <t>129408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>210323</t>
+          <t>211366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245812</t>
+          <t>245648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312203</t>
+          <t>315967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>365492</t>
+          <t>367194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61322</t>
+          <t>60349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91780</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28334</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>51957</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96936</t>
+          <t>96711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>132773</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137661</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175637</t>
+          <t>173515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78022</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>111257</t>
+          <t>110027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225822</t>
+          <t>224965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275433</t>
+          <t>273477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62479</t>
+          <t>63901</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91093</t>
+          <t>90696</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>104699</t>
+          <t>103960</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>133741</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>175246</t>
+          <t>175436</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>214509</t>
+          <t>217090</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19700</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41476</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56257</t>
+          <t>55551</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>88177</t>
+          <t>87147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>819</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>68174</t>
+          <t>68469</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>96505</t>
+          <t>96662</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43873</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70493</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>118031</t>
+          <t>117320</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>157918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3577,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76509</t>
+          <t>78003</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>109290</t>
+          <t>108348</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>177062</t>
+          <t>179343</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>207813</t>
+          <t>209734</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>263977</t>
+          <t>265065</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308419</t>
+          <t>311058</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40784</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65672</t>
+          <t>67771</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>87191</t>
+          <t>88198</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25569</t>
+          <t>25950</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>103469</t>
+          <t>102426</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>133935</t>
+          <t>132894</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44489</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>71342</t>
+          <t>70509</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>153755</t>
+          <t>153271</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>197254</t>
+          <t>195872</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>263136</t>
+          <t>261386</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>312994</t>
+          <t>312660</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>419782</t>
+          <t>419516</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>466952</t>
+          <t>467448</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,12 +4196,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>697912</t>
+          <t>694823</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>770504</t>
+          <t>766380</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>74863</t>
+          <t>75331</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>109889</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>105623</t>
+          <t>104810</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>146760</t>
+          <t>148678</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18860</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>30243</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>200611</t>
+          <t>202593</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>250109</t>
+          <t>250907</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>130975</t>
+          <t>129103</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>173506</t>
+          <t>173673</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>341951</t>
+          <t>344380</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>409335</t>
+          <t>407884</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>259132</t>
+          <t>259435</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>311917</t>
+          <t>313416</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>491526</t>
+          <t>491462</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>545493</t>
+          <t>545296</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>764448</t>
+          <t>768024</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>847355</t>
+          <t>849673</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>122498</t>
+          <t>118365</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>163165</t>
+          <t>162264</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>61804</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>95922</t>
+          <t>95398</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>191651</t>
+          <t>192038</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>244763</t>
+          <t>245296</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>35767</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>29933</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>56124</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>266810</t>
+          <t>267010</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>320897</t>
+          <t>321650</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>147512</t>
+          <t>145580</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>192545</t>
+          <t>191460</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>425031</t>
+          <t>423598</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>499013</t>
+          <t>496129</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1203141</t>
+          <t>1205655</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1316105</t>
+          <t>1315444</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2202130</t>
+          <t>2206620</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2308664</t>
+          <t>2314695</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3439197</t>
+          <t>3434129</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3600392</t>
+          <t>3602434</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>584210</t>
+          <t>582012</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>674534</t>
+          <t>674906</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>227951</t>
+          <t>226717</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>286169</t>
+          <t>289190</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>831198</t>
+          <t>837182</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>939920</t>
+          <t>943162</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>70808</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>106217</t>
+          <t>103429</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>68090</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>102893</t>
+          <t>102122</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>145101</t>
+          <t>143237</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>197464</t>
+          <t>196376</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1246038</t>
+          <t>1244689</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1358779</t>
+          <t>1356023</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>734624</t>
+          <t>733772</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>826978</t>
+          <t>830312</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2001220</t>
+          <t>2007914</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2163486</t>
+          <t>2158918</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61284</t>
+          <t>63313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93153</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129955</t>
+          <t>130647</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>165771</t>
+          <t>167154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>201383</t>
+          <t>201852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251552</t>
+          <t>250671</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66553</t>
+          <t>66258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98026</t>
+          <t>97014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28690</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>53926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100563</t>
+          <t>103694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141257</t>
+          <t>142738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27489</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109066</t>
+          <t>109225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>144525</t>
+          <t>143295</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108304</t>
+          <t>109037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191318</t>
+          <t>193082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>241338</t>
+          <t>241882</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149428</t>
+          <t>148529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>194734</t>
+          <t>192113</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>283484</t>
+          <t>286494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>331475</t>
+          <t>333713</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>447929</t>
+          <t>447371</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>514645</t>
+          <t>514836</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6743,12 +6743,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106688</t>
+          <t>107210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148575</t>
+          <t>146149</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50910</t>
+          <t>47757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81975</t>
+          <t>78428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167358</t>
+          <t>164246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217417</t>
+          <t>218388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14309</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>34875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169780</t>
+          <t>174523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218029</t>
+          <t>220646</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>124052</t>
+          <t>123241</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166595</t>
+          <t>165819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307216</t>
+          <t>301575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>368086</t>
+          <t>367154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -7227,12 +7227,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91627</t>
+          <t>91234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125605</t>
+          <t>127470</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7262,12 +7262,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197974</t>
+          <t>201525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235930</t>
+          <t>238351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300152</t>
+          <t>299862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351090</t>
+          <t>353633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72696</t>
+          <t>74203</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>105480</t>
+          <t>105883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47797</t>
+          <t>49052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>104381</t>
+          <t>103096</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>143900</t>
+          <t>143116</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23358</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101824</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137180</t>
+          <t>134995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66722</t>
+          <t>65039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100536</t>
+          <t>98008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>176289</t>
+          <t>174125</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225113</t>
+          <t>225620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116369</t>
+          <t>118822</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>155916</t>
+          <t>157409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>218074</t>
+          <t>217734</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>256706</t>
+          <t>256925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>347562</t>
+          <t>347942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>405101</t>
+          <t>403211</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88073</t>
+          <t>88182</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125692</t>
+          <t>124783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34449</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59983</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129990</t>
+          <t>131151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>174861</t>
+          <t>174727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19676</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11967</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30641</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103384</t>
+          <t>100293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140079</t>
+          <t>138616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>81161</t>
+          <t>80636</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115464</t>
+          <t>114411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194796</t>
+          <t>192635</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247554</t>
+          <t>244151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56782</t>
+          <t>56858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84789</t>
+          <t>86194</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114783</t>
+          <t>112510</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>143046</t>
+          <t>142358</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>175418</t>
+          <t>178429</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>219060</t>
+          <t>220669</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38990</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64862</t>
+          <t>65371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38673</t>
+          <t>37399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61576</t>
+          <t>61555</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93816</t>
+          <t>95986</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9720</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72486</t>
+          <t>73102</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>103205</t>
+          <t>104760</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>48619</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>75907</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>130801</t>
+          <t>130104</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>170752</t>
+          <t>171642</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>87651</t>
+          <t>88812</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>123138</t>
+          <t>122194</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>174671</t>
+          <t>176206</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>205671</t>
+          <t>205708</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271697</t>
+          <t>272438</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>319419</t>
+          <t>320078</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,77%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71196</t>
+          <t>72592</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102703</t>
+          <t>102808</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>89369</t>
+          <t>88904</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>127575</t>
+          <t>126000</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>26838</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>61820</t>
+          <t>62334</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>92190</t>
+          <t>92818</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>46317</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>72891</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>115138</t>
+          <t>115308</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>154746</t>
+          <t>156922</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -9503,12 +9503,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>187341</t>
+          <t>186078</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>239777</t>
+          <t>236818</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9538,12 +9538,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>380274</t>
+          <t>378351</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>434396</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>580690</t>
+          <t>583215</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>654673</t>
+          <t>655757</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9588,12 +9588,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>147138</t>
+          <t>148512</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>194440</t>
+          <t>192694</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>74998</t>
+          <t>74190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>112528</t>
+          <t>111683</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>231367</t>
+          <t>236252</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>295894</t>
+          <t>295298</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14328</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>31466</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>60653</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>229736</t>
+          <t>232500</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>285693</t>
+          <t>283547</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>151143</t>
+          <t>149838</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>197532</t>
+          <t>197279</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>395463</t>
+          <t>396356</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>465384</t>
+          <t>465322</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -10072,12 +10072,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>321806</t>
+          <t>320968</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>379592</t>
+          <t>380241</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>519870</t>
+          <t>518702</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>573281</t>
+          <t>574197</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -10142,12 +10142,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>857980</t>
+          <t>855373</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>937076</t>
+          <t>937994</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,59%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>108898</t>
+          <t>111117</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>155403</t>
+          <t>157545</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>52319</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>85210</t>
+          <t>85521</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>171930</t>
+          <t>173651</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>228198</t>
+          <t>229707</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27745</t>
+          <t>27550</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>251848</t>
+          <t>252228</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>306470</t>
+          <t>308463</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>178072</t>
+          <t>174300</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>227275</t>
+          <t>228532</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>442422</t>
+          <t>442321</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>516546</t>
+          <t>521567</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1174886</t>
+          <t>1175351</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1295126</t>
+          <t>1290464</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10656,12 +10656,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2127896</t>
+          <t>2125703</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2245641</t>
+          <t>2244080</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3339155</t>
+          <t>3330702</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3508414</t>
+          <t>3507018</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>787449</t>
+          <t>790521</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>889698</t>
+          <t>897288</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>355637</t>
+          <t>356689</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>430250</t>
+          <t>432704</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1170752</t>
+          <t>1168450</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1299146</t>
+          <t>1294079</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>76667</t>
+          <t>78393</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>116998</t>
+          <t>118700</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>55338</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>91729</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>145511</t>
+          <t>145453</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>199524</t>
+          <t>200753</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1208657</t>
+          <t>1198658</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1318921</t>
+          <t>1311748</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>846545</t>
+          <t>845238</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>954179</t>
+          <t>955866</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2085102</t>
+          <t>2086356</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2241909</t>
+          <t>2242424</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11065,12 +11065,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -11446,12 +11446,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88679</t>
+          <t>89451</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>123961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11481,12 +11481,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>143183</t>
+          <t>142452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177593</t>
+          <t>178788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240308</t>
+          <t>241756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>291676</t>
+          <t>290829</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -11559,12 +11559,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64543</t>
+          <t>63125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95727</t>
+          <t>94165</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11574,12 +11574,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11594,12 +11594,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68685</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11609,12 +11609,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11629,12 +11629,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112158</t>
+          <t>114614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154059</t>
+          <t>155750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -11785,12 +11785,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81532</t>
+          <t>82015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116061</t>
+          <t>115651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11800,12 +11800,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>52013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80028</t>
+          <t>80506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141507</t>
+          <t>141666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184514</t>
+          <t>184383</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>228072</t>
+          <t>230713</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12050,12 +12050,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>316887</t>
+          <t>315493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>361242</t>
+          <t>360960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12085,12 +12085,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>516454</t>
+          <t>512789</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>580385</t>
+          <t>580730</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,79%</t>
         </is>
       </c>
     </row>
@@ -12128,12 +12128,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69477</t>
+          <t>69234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103827</t>
+          <t>105840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>52277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102093</t>
+          <t>104339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144932</t>
+          <t>148101</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12213,12 +12213,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -12241,12 +12241,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -12354,12 +12354,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170179</t>
+          <t>174279</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>217166</t>
+          <t>217466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116143</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158200</t>
+          <t>156564</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>304525</t>
+          <t>300837</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>361782</t>
+          <t>362750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12439,12 +12439,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -12584,12 +12584,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134949</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170109</t>
+          <t>171435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206365</t>
+          <t>207657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240724</t>
+          <t>241493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>351995</t>
+          <t>351903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>400913</t>
+          <t>400647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,18%</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56504</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84395</t>
+          <t>87100</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20576</t>
+          <t>20607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40949</t>
+          <t>40137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>83321</t>
+          <t>84482</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119078</t>
+          <t>118636</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12782,12 +12782,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -12810,12 +12810,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12895,12 +12895,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -12923,12 +12923,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73949</t>
+          <t>73364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>106609</t>
+          <t>104069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12938,12 +12938,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>92217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12973,12 +12973,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143409</t>
+          <t>142825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>186373</t>
+          <t>186202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13008,12 +13008,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -13153,12 +13153,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>110710</t>
+          <t>111255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>148807</t>
+          <t>147476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206854</t>
+          <t>203806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247618</t>
+          <t>243384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>329792</t>
+          <t>329671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>384924</t>
+          <t>388660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13238,12 +13238,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -13266,12 +13266,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82791</t>
+          <t>80949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114787</t>
+          <t>116447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>38960</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64607</t>
+          <t>65592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13316,47 +13316,47 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>148525</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>126565</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>171702</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>16,74%</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>148525</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>127226</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>173284</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -13379,12 +13379,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13394,12 +13394,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>21337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13429,12 +13429,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13449,12 +13449,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -13492,12 +13492,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115868</t>
+          <t>115246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>154370</t>
+          <t>150633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13507,12 +13507,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13527,12 +13527,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78706</t>
+          <t>79289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114904</t>
+          <t>114462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13562,12 +13562,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201456</t>
+          <t>200127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254799</t>
+          <t>252927</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13577,12 +13577,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -13722,12 +13722,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>69055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94964</t>
+          <t>95848</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126100</t>
+          <t>126440</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154015</t>
+          <t>153496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>200079</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241819</t>
+          <t>242614</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13807,12 +13807,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -13835,12 +13835,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>55262</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13870,12 +13870,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14041</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51391</t>
+          <t>51494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>82491</t>
+          <t>81080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13920,12 +13920,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -13948,12 +13948,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14018,12 +14018,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -14061,12 +14061,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66456</t>
+          <t>66854</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>94130</t>
+          <t>94032</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14096,12 +14096,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69422</t>
+          <t>70083</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14111,47 +14111,47 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
+          <t>32,06%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>136504</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>119283</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>155512</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
           <t>31,76%</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>136504</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>117804</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>156476</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>31,76%</t>
-        </is>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14291,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>107464</t>
+          <t>107737</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138687</t>
+          <t>140454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14326,12 +14326,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>166695</t>
+          <t>166684</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>196765</t>
+          <t>197991</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>284782</t>
+          <t>284581</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>327903</t>
+          <t>330646</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,66%</t>
         </is>
       </c>
     </row>
@@ -14404,12 +14404,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39024</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63603</t>
+          <t>64008</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26764</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14474,12 +14474,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>53310</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82930</t>
+          <t>84217</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14489,12 +14489,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14517,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14552,12 +14552,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -14630,12 +14630,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>70498</t>
+          <t>69441</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>100964</t>
+          <t>99155</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14665,12 +14665,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>131382</t>
+          <t>130680</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>172929</t>
+          <t>173519</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -14860,12 +14860,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>292686</t>
+          <t>293236</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>347043</t>
+          <t>349655</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>399516</t>
+          <t>403865</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>449987</t>
+          <t>454795</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14930,12 +14930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>709090</t>
+          <t>714150</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>785011</t>
+          <t>788141</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14945,12 +14945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -14973,12 +14973,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>110496</t>
+          <t>109404</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>152296</t>
+          <t>153422</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15008,12 +15008,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69718</t>
+          <t>70005</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>105026</t>
+          <t>106735</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>192289</t>
+          <t>191652</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>247682</t>
+          <t>251532</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -15058,12 +15058,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -15086,12 +15086,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12234</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>30714</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33955</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>30988</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>58163</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -15199,12 +15199,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>157626</t>
+          <t>157951</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>204165</t>
+          <t>205570</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>131434</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>174231</t>
+          <t>174696</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>301095</t>
+          <t>299274</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>368335</t>
+          <t>366607</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>353266</t>
+          <t>354055</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>413578</t>
+          <t>410015</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>495769</t>
+          <t>495771</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>552576</t>
+          <t>554132</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15499,12 +15499,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>867998</t>
+          <t>865180</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>947181</t>
+          <t>944328</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -15514,12 +15514,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -15542,12 +15542,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>119377</t>
+          <t>119065</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>168070</t>
+          <t>163916</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -15557,12 +15557,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15577,12 +15577,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>71270</t>
+          <t>70570</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>109203</t>
+          <t>107494</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>200174</t>
+          <t>200081</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>257220</t>
+          <t>258074</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -15655,12 +15655,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>13170</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31230</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -15670,12 +15670,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>42919</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>209440</t>
+          <t>210938</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>263021</t>
+          <t>262254</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15783,12 +15783,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15803,12 +15803,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>181056</t>
+          <t>180391</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>229852</t>
+          <t>234066</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>404796</t>
+          <t>402708</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>476639</t>
+          <t>478029</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1442904</t>
+          <t>1444112</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1559712</t>
+          <t>1557913</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16033,12 +16033,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2173783</t>
+          <t>2164458</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2285609</t>
+          <t>2283747</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3647684</t>
+          <t>3646447</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3820062</t>
+          <t>3819124</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -16111,12 +16111,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>654103</t>
+          <t>646471</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>747566</t>
+          <t>742836</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -16126,12 +16126,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16146,12 +16146,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1022622</t>
+          <t>1024460</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1149943</t>
+          <t>1147058</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -16224,12 +16224,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>76616</t>
+          <t>75516</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>113295</t>
+          <t>115618</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -16239,12 +16239,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16259,12 +16259,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>143390</t>
+          <t>142110</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>196425</t>
+          <t>194902</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -16337,12 +16337,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1038811</t>
+          <t>1047905</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1152918</t>
+          <t>1151993</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -16352,12 +16352,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16372,12 +16372,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>797859</t>
+          <t>800513</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>901243</t>
+          <t>906500</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -16387,12 +16387,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16407,12 +16407,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1866753</t>
+          <t>1869301</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2020665</t>
+          <t>2022766</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
